--- a/data/EQUI.MI.xlsx
+++ b/data/EQUI.MI.xlsx
@@ -51719,7 +51719,7 @@
         <v>6</v>
       </c>
       <c r="D2233" t="n">
-        <v>5.78000020980835</v>
+        <v>5.73999977111816</v>
       </c>
       <c r="E2233" t="n">
         <v>5.80999994277954</v>
@@ -51728,6 +51728,29 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G2233" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2234">
+      <c r="A2234" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2234" t="n">
+        <v>77220</v>
+      </c>
+      <c r="C2234" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="D2234" t="n">
+        <v>5.71999979019165</v>
+      </c>
+      <c r="E2234" t="n">
+        <v>5.73999977111816</v>
+      </c>
+      <c r="F2234" t="n">
+        <v>5.82000017166138</v>
+      </c>
+      <c r="G2234" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EQUI.MI.xlsx
+++ b/data/EQUI.MI.xlsx
@@ -51754,6 +51754,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2235">
+      <c r="A2235" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2235" t="n">
+        <v>29292</v>
+      </c>
+      <c r="C2235" t="n">
+        <v>5.8899998664856</v>
+      </c>
+      <c r="D2235" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="E2235" t="n">
+        <v>5.76999998092651</v>
+      </c>
+      <c r="F2235" t="n">
+        <v>5.8600001335144</v>
+      </c>
+      <c r="G2235" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EQUI.MI.xlsx
+++ b/data/EQUI.MI.xlsx
@@ -51777,6 +51777,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2236">
+      <c r="A2236" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2236" t="n">
+        <v>114531</v>
+      </c>
+      <c r="C2236" t="n">
+        <v>6.1100001335144</v>
+      </c>
+      <c r="D2236" t="n">
+        <v>5.94000005722046</v>
+      </c>
+      <c r="E2236" t="n">
+        <v>6.01999998092651</v>
+      </c>
+      <c r="F2236" t="n">
+        <v>5.94000005722046</v>
+      </c>
+      <c r="G2236" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EQUI.MI.xlsx
+++ b/data/EQUI.MI.xlsx
@@ -51800,6 +51800,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2237">
+      <c r="A2237" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2237" t="n">
+        <v>109969</v>
+      </c>
+      <c r="C2237" t="n">
+        <v>6.17999982833862</v>
+      </c>
+      <c r="D2237" t="n">
+        <v>5.98000001907349</v>
+      </c>
+      <c r="E2237" t="n">
+        <v>5.98999977111816</v>
+      </c>
+      <c r="F2237" t="n">
+        <v>6.01999998092651</v>
+      </c>
+      <c r="G2237" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EQUI.MI.xlsx
+++ b/data/EQUI.MI.xlsx
@@ -51641,22 +51641,22 @@
     </row>
     <row r="2230">
       <c r="A2230" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2230" t="n">
-        <v>21962</v>
+        <v>56432</v>
       </c>
       <c r="C2230" t="n">
-        <v>5.8899998664856</v>
+        <v>5.88000011444092</v>
       </c>
       <c r="D2230" t="n">
-        <v>5.78999996185303</v>
+        <v>5.78000020980835</v>
       </c>
       <c r="E2230" t="n">
-        <v>5.80000019073486</v>
+        <v>5.84000015258789</v>
       </c>
       <c r="F2230" t="n">
-        <v>5.84999990463257</v>
+        <v>5.84000015258789</v>
       </c>
       <c r="G2230" t="s">
         <v>7</v>
@@ -51664,22 +51664,22 @@
     </row>
     <row r="2231">
       <c r="A2231" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2231" t="n">
-        <v>36519</v>
+        <v>21962</v>
       </c>
       <c r="C2231" t="n">
-        <v>5.8600001335144</v>
+        <v>5.8899998664856</v>
       </c>
       <c r="D2231" t="n">
-        <v>5.76999998092651</v>
+        <v>5.78999996185303</v>
       </c>
       <c r="E2231" t="n">
-        <v>5.8600001335144</v>
+        <v>5.80000019073486</v>
       </c>
       <c r="F2231" t="n">
-        <v>5.78999996185303</v>
+        <v>5.84999990463257</v>
       </c>
       <c r="G2231" t="s">
         <v>7</v>
@@ -51687,22 +51687,22 @@
     </row>
     <row r="2232">
       <c r="A2232" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2232" t="n">
-        <v>39736</v>
+        <v>36519</v>
       </c>
       <c r="C2232" t="n">
-        <v>5.86999988555908</v>
+        <v>5.8600001335144</v>
       </c>
       <c r="D2232" t="n">
-        <v>5.73999977111816</v>
+        <v>5.76999998092651</v>
       </c>
       <c r="E2232" t="n">
-        <v>5.80999994277954</v>
+        <v>5.8600001335144</v>
       </c>
       <c r="F2232" t="n">
-        <v>5.73999977111816</v>
+        <v>5.78999996185303</v>
       </c>
       <c r="G2232" t="s">
         <v>7</v>
@@ -51710,13 +51710,13 @@
     </row>
     <row r="2233">
       <c r="A2233" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2233" t="n">
-        <v>123284</v>
+        <v>39736</v>
       </c>
       <c r="C2233" t="n">
-        <v>6</v>
+        <v>5.86999988555908</v>
       </c>
       <c r="D2233" t="n">
         <v>5.73999977111816</v>
@@ -51733,22 +51733,22 @@
     </row>
     <row r="2234">
       <c r="A2234" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2234" t="n">
-        <v>77220</v>
+        <v>123284</v>
       </c>
       <c r="C2234" t="n">
-        <v>5.90000009536743</v>
+        <v>6</v>
       </c>
       <c r="D2234" t="n">
-        <v>5.71999979019165</v>
+        <v>5.73999977111816</v>
       </c>
       <c r="E2234" t="n">
+        <v>5.80999994277954</v>
+      </c>
+      <c r="F2234" t="n">
         <v>5.73999977111816</v>
-      </c>
-      <c r="F2234" t="n">
-        <v>5.82000017166138</v>
       </c>
       <c r="G2234" t="s">
         <v>7</v>
@@ -51756,22 +51756,22 @@
     </row>
     <row r="2235">
       <c r="A2235" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2235" t="n">
-        <v>29292</v>
+        <v>77220</v>
       </c>
       <c r="C2235" t="n">
-        <v>5.8899998664856</v>
+        <v>5.90000009536743</v>
       </c>
       <c r="D2235" t="n">
-        <v>5.75</v>
+        <v>5.71999979019165</v>
       </c>
       <c r="E2235" t="n">
-        <v>5.76999998092651</v>
+        <v>5.73999977111816</v>
       </c>
       <c r="F2235" t="n">
-        <v>5.8600001335144</v>
+        <v>5.82000017166138</v>
       </c>
       <c r="G2235" t="s">
         <v>7</v>
@@ -51779,22 +51779,22 @@
     </row>
     <row r="2236">
       <c r="A2236" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2236" t="n">
-        <v>114531</v>
+        <v>29292</v>
       </c>
       <c r="C2236" t="n">
-        <v>6.1100001335144</v>
+        <v>5.8899998664856</v>
       </c>
       <c r="D2236" t="n">
-        <v>5.94000005722046</v>
+        <v>5.75</v>
       </c>
       <c r="E2236" t="n">
-        <v>6.01999998092651</v>
+        <v>5.76999998092651</v>
       </c>
       <c r="F2236" t="n">
-        <v>5.94000005722046</v>
+        <v>5.8600001335144</v>
       </c>
       <c r="G2236" t="s">
         <v>7</v>
@@ -51802,24 +51802,47 @@
     </row>
     <row r="2237">
       <c r="A2237" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2237" t="n">
-        <v>109969</v>
+        <v>114531</v>
       </c>
       <c r="C2237" t="n">
-        <v>6.17999982833862</v>
+        <v>6.1100001335144</v>
       </c>
       <c r="D2237" t="n">
+        <v>5.94000005722046</v>
+      </c>
+      <c r="E2237" t="n">
+        <v>6.01999998092651</v>
+      </c>
+      <c r="F2237" t="n">
+        <v>5.94000005722046</v>
+      </c>
+      <c r="G2237" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2238">
+      <c r="A2238" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2238" t="n">
+        <v>35116</v>
+      </c>
+      <c r="C2238" t="n">
+        <v>6.07999992370605</v>
+      </c>
+      <c r="D2238" t="n">
         <v>5.98000001907349</v>
       </c>
-      <c r="E2237" t="n">
-        <v>5.98999977111816</v>
-      </c>
-      <c r="F2237" t="n">
+      <c r="E2238" t="n">
         <v>6.01999998092651</v>
       </c>
-      <c r="G2237" t="s">
+      <c r="F2238" t="n">
+        <v>6.03999996185303</v>
+      </c>
+      <c r="G2238" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EQUI.MI.xlsx
+++ b/data/EQUI.MI.xlsx
@@ -52115,8 +52115,31 @@
       <c r="E2250" t="n">
         <v>5.80999994277954</v>
       </c>
-      <c r="F2250"/>
+      <c r="F2250" t="n">
+        <v>5.94999980926514</v>
+      </c>
       <c r="G2250" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2251">
+      <c r="A2251" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2251" t="n">
+        <v>28494</v>
+      </c>
+      <c r="C2251" t="n">
+        <v>6.03999996185303</v>
+      </c>
+      <c r="D2251" t="n">
+        <v>5.98000001907349</v>
+      </c>
+      <c r="E2251" t="n">
+        <v>5.98000001907349</v>
+      </c>
+      <c r="F2251"/>
+      <c r="G2251" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EQUI.MI.xlsx
+++ b/data/EQUI.MI.xlsx
@@ -52138,8 +52138,31 @@
       <c r="E2251" t="n">
         <v>5.98000001907349</v>
       </c>
-      <c r="F2251"/>
+      <c r="F2251" t="n">
+        <v>6.01999998092651</v>
+      </c>
       <c r="G2251" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2252">
+      <c r="A2252" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2252" t="n">
+        <v>35929</v>
+      </c>
+      <c r="C2252" t="n">
+        <v>6.05999994277954</v>
+      </c>
+      <c r="D2252" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="E2252" t="n">
+        <v>6.05999994277954</v>
+      </c>
+      <c r="F2252"/>
+      <c r="G2252" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EQUI.MI.xlsx
+++ b/data/EQUI.MI.xlsx
@@ -52161,8 +52161,31 @@
       <c r="E2252" t="n">
         <v>6.05999994277954</v>
       </c>
-      <c r="F2252"/>
+      <c r="F2252" t="n">
+        <v>5.92000007629395</v>
+      </c>
       <c r="G2252" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2253">
+      <c r="A2253" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2253" t="n">
+        <v>42185</v>
+      </c>
+      <c r="C2253" t="n">
+        <v>5.98000001907349</v>
+      </c>
+      <c r="D2253" t="n">
+        <v>5.84999990463257</v>
+      </c>
+      <c r="E2253" t="n">
+        <v>5.96000003814697</v>
+      </c>
+      <c r="F2253"/>
+      <c r="G2253" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EQUI.MI.xlsx
+++ b/data/EQUI.MI.xlsx
@@ -52184,8 +52184,31 @@
       <c r="E2253" t="n">
         <v>5.96000003814697</v>
       </c>
-      <c r="F2253"/>
+      <c r="F2253" t="n">
+        <v>5.96999979019165</v>
+      </c>
       <c r="G2253" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2254">
+      <c r="A2254" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2254" t="n">
+        <v>33568</v>
+      </c>
+      <c r="C2254" t="n">
+        <v>6.03999996185303</v>
+      </c>
+      <c r="D2254" t="n">
+        <v>5.98000001907349</v>
+      </c>
+      <c r="E2254" t="n">
+        <v>5.98999977111816</v>
+      </c>
+      <c r="F2254"/>
+      <c r="G2254" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EQUI.MI.xlsx
+++ b/data/EQUI.MI.xlsx
@@ -52214,6 +52214,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2255">
+      <c r="A2255" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2255" t="n">
+        <v>36940</v>
+      </c>
+      <c r="C2255" t="n">
+        <v>6.05999994277954</v>
+      </c>
+      <c r="D2255" t="n">
+        <v>5.98000001907349</v>
+      </c>
+      <c r="E2255" t="n">
+        <v>6.05999994277954</v>
+      </c>
+      <c r="F2255" t="n">
+        <v>6.03999996185303</v>
+      </c>
+      <c r="G2255" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
